--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0032.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0032.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Novelty: Uses</t>
+          <t>Mới Lạ: Số Lần Sử Dụng</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Battle Stage</t>
+          <t>Giai Đoạn Chiến Đấu</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Echo Cốt lõi</t>
+          <t>Tiếng Vọng Cốt Lõi</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Số lượng Echoes Cost 1 trong bộ bài của bạn đã đạt giới hạn</t>
+          <t>Số lượng Echo Cost 1 trong bộ bài của bạn đã đạt giới hạn</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Không có Echoes nào có thể xóa</t>
+          <t>Không có Echo nào có thể xóa</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Glory Unwept</t>
+          <t>Vinh Quang Không Nước Mắt</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Thousand Island Aftertune</t>
+          <t>Khúc Hoà Tấu Sau Ngàn Đảo</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Summer's End</t>
+          <t>Cuối Hạ</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Hoàn thành Khi As the Bamboo Leaf Falls - Thường Mode</t>
+          <t>Hoàn thành Khi Lá Tre Rơi - Chế Độ Thường</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Hoàn thành The Hour of Hope - Chế độ Thường</t>
+          <t>Hoàn thành Giờ Khắc Hy Vọng - Chế độ Thường</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Hoàn thành Dance Qingloong - Chế độ Thường</t>
+          <t>Hoàn thành Vũ Điệu Thanh Long - Chế độ Thường</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Hoàn thành Phantom of the Beyond - Thường Mode</t>
+          <t>Hoàn thành Phantom of the Beyond - Chế Độ Thường</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Complete Crimson Waltz - Thường Mode</t>
+          <t>Hoàn thành Vũ Điệu Đỏ Thẫm - Chế độ Thường</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Hoàn thành Bright Moon Trong Đêm Tối - Thường Mode</t>
+          <t>Hoàn thành Trăng Sáng Trong Đêm Tối - Chế Độ Thường</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Hoàn thành Khi As the Bamboo Leaf Falls - Chế Độ Khó</t>
+          <t>Hoàn thành Khi Lá Tre Rơi - Chế Độ Khó</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Hoàn thành The Hour of Hope - Chế độ Khó</t>
+          <t>Hoàn thành Giờ Khắc Hy Vọng - Chế độ Khó</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Hoàn thành Dance Qingloong - Chế độ Khó</t>
+          <t>Hoàn thành Vũ Điệu Thanh Long - Chế độ Khó</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Complete Crimson Waltz - Khó Mode</t>
+          <t>Hoàn thành Vũ Điệu Đỏ Thẫm - Chế độ Khó</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Hoàn thành Bright Moon Trong Đêm Tối - Chế Độ Khó</t>
+          <t>Hoàn thành Trăng Sáng Trong Đêm Tối - Chế Độ Khó</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Thường Mode Rewards</t>
+          <t>Phần Thưởng Chế Độ Thường</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Khó Mode Rewards</t>
+          <t>Phần Thưởng Chế Độ Khó</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Deep Sea Survey I</t>
+          <t>Khảo Sát Vực Sâu I</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Deep Sea Survey II</t>
+          <t>Khảo Sát Vực Sâu II</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Deep Sea Survey III</t>
+          <t>Khảo Sát Vực Sâu III</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Deep Sea Survey IV</t>
+          <t>Khảo Sát Vực Sâu IV</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Deep Sea Survey V</t>
+          <t>Khảo Sát Vực Sâu V</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Deep Sea Survey VI</t>
+          <t>Khảo Sát Vực Sâu VI</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Prints of Plateaus I</t>
+          <t>Dấu Vết Cao Nguyên I</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Prints of Plateaus II</t>
+          <t>Dấu Vết Cao Nguyên II</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Prints of Plateaus III</t>
+          <t>Dấu Vết Cao Nguyên III</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Prints of Plateaus IV</t>
+          <t>Dấu Vết Cao Nguyên IV</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Prints of Plateaus V</t>
+          <t>Dấu Vết Cao Nguyên V</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Prints of Plateaus VI</t>
+          <t>Dấu Vết Cao Nguyên VI</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Whispers of the Waves I</t>
+          <t>Lời thì thầm của sóng biển I</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Whispers of the Waves II</t>
+          <t>Lời Thì Thầm Của Sóng II</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Whispers of the Waves III</t>
+          <t>Lời Thì Thầm Của Sóng III</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Whispers of the Waves IV</t>
+          <t>Lời Thì Thầm Của Sóng IV</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Whispers of the Waves V</t>
+          <t>Lời Thì Thầm Của Sóng V</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Whispers of the Waves VI</t>
+          <t>Lời Thì Thầm Của Sóng VI</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Honami City</t>
+          <t>Thành Phố Honami</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Capturing Starlight I</t>
+          <t>Ghi lại Ánh Sao I</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Capturing Starlight II</t>
+          <t>Ghi lại Ánh Sao II</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Capturing Starlight III</t>
+          <t>Thu Ánh Sao III</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Capturing Starlight IV</t>
+          <t>Thu Ánh Sao IV</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Capturing Starlight V</t>
+          <t>Thu Ánh Sao V</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Capturing Starlight VI</t>
+          <t>Thu Ánh Sao VI</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Capturing Starlight VII</t>
+          <t>Thu Ánh Sao VII</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Capturing Starlight VIII</t>
+          <t>Thu Ánh Sao VIII</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Capturing Starlight IX</t>
+          <t>Thu Ánh Sao IX</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Capture the first frame</t>
+          <t>Ghi lại khung hình đầu tiên</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Capture the second frame</t>
+          <t>Ghi lại khung hình thứ hai</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Capture the third frame</t>
+          <t>Chụp khung hình thứ ba</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Sử dụng Instant Veto</t>
+          <t>Dùng Instant Veto.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Sử dụng Instant Veto</t>
+          <t>Dùng Instant Veto.</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Sử dụng Instant Veto</t>
+          <t>Dùng Instant Veto.</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Chương III Act III</t>
+          <t>Chương III Hồi III</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Ngôi Sao Hành Hương Xa</t>
+          <t>Ngôi Sao Viễn Du</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Dreamcatcher tại Khu Vườn Bí Mật</t>
+          <t>Những Kẻ Bắt Giấc Mơ Trong Vườn Bí Mật</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Chương II Act VII</t>
+          <t>Chương II Hồi VII</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Bằng Bàn Tay Cháy Bỏng Của Mặt Trời</t>
+          <t>Bởi Bàn Tay Rực Cháy của Mặt Trời</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Chương II Act VIII</t>
+          <t>Chương II Hồi VIII</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Dawn Trên Bóng Tối Dâng Trào</t>
+          <t>Bình Minh Trên Bóng Tối Dâng Trào</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Chương II Act X &amp; XI</t>
+          <t>Chương II Hồi X &amp; XI</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Dawn Trì Trệ trên Vùng Đất Hoang</t>
+          <t>Bình Minh Trì Trệ trên Vùng Đất Hoang</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Chương II Act XII</t>
+          <t>Chương II Hồi XII</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Điều Gì Cháy Dưới Vùng Đất Băng Giá</t>
+          <t>Điều Gì Nung Nấu Dưới Lãnh Nguyên Băng Giá</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Chương III Act I</t>
+          <t>Chương III Hồi I</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Mở khóa Reprise Bounty để nhận các phần thưởng sau</t>
+          <t>Mở khóa Nhiệm Vụ Encore để nhận những phần thưởng sau.</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Tune Rupture Response</t>
+          <t>Phản ứng Tune Rupture</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Tune Break Boost</t>
+          <t>Tăng cường Đột phá Điệu nhạc</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Off-Tune Buildup Efficiency</t>
+          <t>Hiệu Suất Tích Lũy Lệch Tần</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Solis Tavern</t>
+          <t>Quán Rượu Solis</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>The Silver Helmet</t>
+          <t>Mũ Bạc</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Steward's Supply Station</t>
+          <t>Trạm cung ứng của Quản gia</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Brightness successfully adjusted</t>
+          <t>Đã điều chỉnh độ sáng thành công</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Tất cả Materials</t>
+          <t>Tất cả Nguyên liệu</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Resonator Materials</t>
+          <t>Vật Liệu Resonator</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>EXP Vật phẩm</t>
+          <t>Vật phẩm Kinh Nghiệm</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Weapon Materials</t>
+          <t>Vật Liệu Vũ Khí</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>First Stage</t>
+          <t>Giai Đoạn Đầu Tiên</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Second Stage</t>
+          <t>Giai Đoạn Hai</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Third Stage</t>
+          <t>Giai Đoạn Ba</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Fourth Stage</t>
+          <t>Giai Đoạn Bốn</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Fifth Stage</t>
+          <t>Giai Đoạn Năm</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Equip Vũ Khí 3-Star trở lên</t>
+          <t>Trang bị Vũ Khí 3 Sao trở lên</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Complete Nhiệm Vụ Chính: Echoing Marche</t>
+          <t>Hoàn thành Nhiệm Vụ Chính: Echoing Marche</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Mở 10 Rương Cung Ứng</t>
+          <t>Mở 10 Rương Cung Cấp</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Complete Nhiệm Vụ Chính: Ominous Star</t>
+          <t>Hoàn thành Nhiệm Vụ Chính: Ngôi Sao Oan Nghiệt</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Hoàn thành Basic Training 1 lần</t>
+          <t>Hoàn thành Huấn Luyện Cơ Bản 1 lần</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Hấp thu 10 Dư Âm từ 2-Star trở lên</t>
+          <t>Hấp thu 10 Dư Âm từ 2 Sao trở lên</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Kích hoạt bất kỳ Sonata Effect nào trên 1 Resonator.</t>
+          <t>Kích hoạt bất kỳ Hiệu Ứng Sonata nào trên 1 Resonator.</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Mua 1 món đồ từ Souvenir Cửa hàng</t>
+          <t>Mua 1 món đồ từ Cửa Hàng Lưu Niệm</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Complete Nhiệm Vụ Chính: Clashing Blades</t>
+          <t>Hoàn thành Nhiệm Vụ Chính: Kiếm Khí Chạm Trán</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Cook 2 Dishes</t>
+          <t>Nấu 2 Món</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Nhận được 3 Huy Hiệu trong Resonant Tower ở Tower Thử Thách: Vùng Ổn Định.</t>
+          <t>Nhận được 3 Huy Hiệu trong Tháp Cộng Hưởng ở Tháp Thử Thách: Vùng Ổn Định.</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Tổng cộng 3 Echoes Tune nhạc</t>
+          <t>Tổng cộng 3 Echo Điệu nhạc</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Hoàn thành Challenges Giả Mạo 2 lần</t>
+          <t>Hoàn thành Thử Thách Giả Mạo 2 lần</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Hấp thu 10 Dư Âm từ 3-Star trở lên</t>
+          <t>Hấp thu 10 Dư Âm từ 3 Sao trở lên</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Hoàn thành Tacet Suppression 1 lần.</t>
+          <t>Hoàn thành Đàn Áp Tacet 1 lần.</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Hấp thụ 5 Echoes hiếm cấp 4-Star trở lên</t>
+          <t>Hấp thụ 5 Echo hiếm cấp 4 Sao trở lên</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Hoàn thành Tactical Hologram: Calamity - Impermanence Heron I</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Impermanence Heron I</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Hoàn thành Weekly Challenge: Sinful Declension 1 lần</t>
+          <t>Hoàn thành Thử Thách Hàng Tuần: Sinful Declension 1 lần</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Tổng cộng 5 Echoes Tune nhạc</t>
+          <t>Tổng cộng 5 Echo Điệu nhạc</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Thu thập 12 Huy Hiệu tại Resonant Tower trong Tower Thử Thách: Stable Zone</t>
+          <t>Thu thập 12 Huy Hiệu tại Tháp Cộng Hưởng trong Tháp Thử Thách: Khu Vực Ổn Định</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Tổng cộng 10 Echoes Tune nhạc</t>
+          <t>Tổng cộng 10 Echo Điệu nhạc</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Hấp thu 10 Dư Âm từ 4-Star trở lên</t>
+          <t>Hấp thu 10 Dư Âm từ 4 Sao trở lên</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Hoàn thành Tacet Suppression 5 lần.</t>
+          <t>Hoàn thành Đàn Áp Tacet 5 lần.</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Đánh bại Impermanence Heron II trong Tactical Hologram: Calamity</t>
+          <t>Đánh bại Impermanence Heron II trong Chiến Thuật Hologram: Calamity</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Thu thập 6 Huy Hiệu trong Resonant Tower tại Tower Thử Thách: Experiment Zone</t>
+          <t>Thu thập 6 Huy Hiệu trong Tháp Cộng Hưởng tại Tháp Thử Thách: Khu Vực Thí Nghiệm</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Equip 3 Echoes cho bất kỳ Resonator nào</t>
+          <t>Trang bị 3 Echo cho bất kỳ Resonator nào</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Hoàn thành Challenge Boss 1 lần</t>
+          <t>Hoàn thành Thử Thách Trùm 1 lần</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Hấp thu 10 Dư Âm từ 5-Star trở lên</t>
+          <t>Hấp thu 10 Dư Âm từ 5 Sao trở lên</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Thu thập 12 Huy Hiệu tại Resonant Tower trong Tower Thử Thách: Experiment Zone</t>
+          <t>Thu thập 12 Huy Hiệu tại Tháp Cộng Hưởng trong Tháp Thử Thách: Khu Vực Thí Nghiệm</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Hoàn thành Tactical Hologram: Calamity - Crownless III</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Crownless III</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Đạt 30% Exploration Progress tại Quần đảo Bờ Đen và Vực sâu Tethys</t>
+          <t>Đạt 30% Tiến Độ Thám Hiểm tại Quần đảo Bờ Đen và Vực sâu Tethys</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Thu thập 12 Huy Hiệu tại Tower Vang Âm trong Tower Thử Thách: Experiment Zone</t>
+          <t>Thu thập 12 Huy Hiệu tại Tháp Vang Âm trong Tháp Thử Thách: Khu Vực Thí Nghiệm</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Hoàn thành Tactical Hologram: Calamity - Inferno Rider III</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Inferno Rider III</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Spend 500 Premium Tuners</t>
+          <t>Dùng 500 Bộ Điều Chỉnh Cao Cấp.</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Đạt 30% Exploration Progress ở cả 8 khu vực Ragunna</t>
+          <t>Đạt 30% Tiến Độ Thám Hiểm ở cả 8 khu vực Ragunna</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Tactical Hologram Hoàn Chỉnh: Nỗi Đau Ảo - Fallacy of Không Return III.</t>
+          <t>Bản Hologram Chiến Thuật Hoàn Chỉnh: Nỗi Đau Ảo - Ảo Tưởng Vô Hồi III.</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Bạn cannot place Memos mid-battle</t>
+          <t>Bạn không thể đặt Ghi Chú giữa trận chiến.</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>WHICH MEANS</t>
+          <t>ĐIỀU ĐÓ CÓ NGHĨA LÀ</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>THEN</t>
+          <t>THẾ THÌ</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>BUT</t>
+          <t>NHƯNG</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>THẾ NÀO...</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>BESIDES</t>
+          <t>NGOÀI RA</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>HOẶC</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>CỘNG</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>VÀ</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Action Content 1</t>
+          <t>Nội Dung Hành Động 1</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Action Title 1</t>
+          <t>Tiêu Đề Hành Động 1</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Memo from "{PlayerName}"</t>
+          <t>Bản ghi nhớ từ "{PlayerName}"</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>{} AHEAD</t>
+          <t>PHÍA TRƯỚC</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>NO {} AHEAD</t>
+          <t>KHÔNG CÓ {} PHÍA TRƯỚC</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>LIKELY {}</t>
+          <t>CÓ THỂ {}</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>DEFINITELY NOT {}</t>
+          <t>CHẮC CHẮN KHÔNG PHẢI {}</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>ANTICIPATING {}</t>
+          <t>ĐANG CHỜ ĐỢI {}</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Places &amp; Vật phẩm</t>
+          <t>Địa điểm &amp; Vật phẩm</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Enemies</t>
+          <t>Kẻ Thù</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Directions</t>
+          <t>Chỉ dẫn</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Hành Động</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Organizations</t>
+          <t>Các Tổ Chức</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Phrases</t>
+          <t>Câu Nói</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>GRAPPLE POINT</t>
+          <t>ĐIỂM BÁM</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>AIR DODGE</t>
+          <t>Né Tránh Tự Động</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>PARRY</t>
+          <t>PHÒNG NGỰ</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>TREASURE CHEST</t>
+          <t>RƯƠNG KHO BÁU</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>IMPORTANT ITEM</t>
+          <t>VẬT PHẨM QUAN TRỌNG</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>COOL STUFF</t>
+          <t>ĐỒ CHẤT</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>NGUYÊN LIỆU</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>PLANT</t>
+          <t>THỰC VẬT</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CỔNG</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>PROPULSION FLUX</t>
+          <t>DÒNG XUNG LỰC</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>ELEVATOR</t>
+          <t>THANG MÁY</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>HIDDEN PATH</t>
+          <t>CON ĐƯỜNG ẨN</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>VIEWPOINT</t>
+          <t>GÓC NHÌN</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>RUINS</t>
+          <t>TÀN TÍCH</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>PUZZLES</t>
+          <t>CÂU ĐỐ</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>MUTANT ORGANISM</t>
+          <t>SINH VẬT ĐỘT BIẾN</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>LIAR</t>
+          <t>KẺ DỐI TRÁ</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>EXILES</t>
+          <t>KẺ LƯU ĐÀY</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>STRANGE HUMANOID CREATURE</t>
+          <t>SINH VẬT DẠNG NGƯỜI KỲ LẠ</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>TACET FIELD</t>
+          <t>TỔ TACET</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>CALAMITY CLASS</t>
+          <t>CẤP ĐỘ THẢM HỌA</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>OVERLORD CLASS</t>
+          <t>HẠNG QUÁN QUÂN</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>ELITE CLASS</t>
+          <t>HẠNG ƯU TÚ</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>COMMON CLASS</t>
+          <t>HẠNG PHỔ THÔNG</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>SMALL FRY</t>
+          <t>TIỂU HỒ ĐỒ</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>PHÍA TRƯỚC</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>BACK</t>
+          <t>LÙI</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>LEFT</t>
+          <t>BÊN TRÁI</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>RIGHT</t>
+          <t>Đúng rồi</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>ABOVE</t>
+          <t>PHÍA TRÊN</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>BELOW</t>
+          <t>BÊN DƯỚI</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>MIDDLE</t>
+          <t>TRUNG CẤP</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>EAST</t>
+          <t>PHÍA ĐÔNG</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>SOUTH</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>PHÍA TÂY</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>NORTH</t>
+          <t>BẮC</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>SOUTHEAST</t>
+          <t>ĐÔNG NAM</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>NORTHEAST</t>
+          <t>ĐÔNG BẮC</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>TÂY NAM</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>NORTHWEST</t>
+          <t>TÂY BẮC</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>INSIDE</t>
+          <t>BÊN TRONG</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>JUMP</t>
+          <t>NHẢY</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>LAO VỀ</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>TRACK</t>
+          <t>THEO DÕI</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>ESCAPE</t>
+          <t>THOÁT</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>CROUCH</t>
+          <t>NẰM XUỐNG</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>WALK</t>
+          <t>ĐI BỘ</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>GLIDE</t>
+          <t>LƯỚT</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>DEFEAT</t>
+          <t>TIÊU DIỆT</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>CLEAN UP</t>
+          <t>DỌN DẸP</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>NẤU ĂN</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>MERCHANT</t>
+          <t>NGƯỜI BUÔN BÁN</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>PIONEER ASSOCIATION</t>
+          <t>HIỆP HỘI TIÊN PHONG</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>TAKE SOME REST</t>
+          <t>NGHỈ NGƠI ĐI</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>GO AT IT</t>
+          <t>XÔNG LÊN!</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>PLUNGING ATTACK</t>
+          <t>TẤN CÔNG LAO XUỐNG</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>DON'T GIVE UP</t>
+          <t>ĐỪNG BỎ CUỘC</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>THINK OVER</t>
+          <t>Suy nghĩ kỹ lại đi</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>DON'T STOP</t>
+          <t>ĐỪNG DỪNG LẠI</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>TRY GOING BACK</t>
+          <t>THỬ QUAY LẠI XEM</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>THE VIEW IS GOOD</t>
+          <t>CẢNH ĐẸP THẬT ĐẤY</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>MIGHT SCREW UP</t>
+          <t>CÓ THỂ LÀM HỎNG</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>STAY AWAY</t>
+          <t>TRÁNH RA ĐI</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>HERE</t>
+          <t>TAO ĐÂY</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>LEVITATION</t>
+          <t>TRÔI NỔI</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>GLIDER</t>
+          <t>DÙNG CẤP</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>SENSOR</t>
+          <t>CẢM BIẾN</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Tự Động Chọn</t>
+          <t>Auto Select</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Sigil Lãng Du</t>
+          <t>Ấn Tín Lãng Du</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Sigil</t>
+          <t>Ấn Tín</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Perceptive Eyes</t>
+          <t>Đôi Mắt Nhạy Cảm</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Qingloong</t>
+          <t>Thanh Long</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Mirrors of Clarity</t>
+          <t>Gương Sáng Tâm Minh</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Exploration</t>
+          <t>Thám Hiểm</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Justice Served</t>
+          <t>Công Lý Đã Được Phục Vụ</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Falling Snow</t>
+          <t>Tuyết Rơi</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Napping Time</t>
+          <t>Giờ Ngủ Trưa</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Breeze</t>
+          <t>Cơn Gió Nhẹ</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Healthy Lifestyle</t>
+          <t>Lối sống lành mạnh</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Fairytale</t>
+          <t>Truyện Cổ Tích</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Fangs</t>
+          <t>Nanh Vuốt</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Fiery Dance</t>
+          <t>Điệu Nhảy Lửa</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Crimson Fury</t>
+          <t>Cơn Thịnh Nộ Đỏ Lửa</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Zapstring</t>
+          <t>Dây Sét</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris</t>
+          <t>Thám Sát Âm Than: Lính Solaris</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Jinzhou Records</t>
+          <t>Biên Niên Sử Jinzhou</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>En Route</t>
+          <t>Đang Di Chuyển</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Global Pre-registration</t>
+          <t>Đăng Ký Trước Toàn Cầu</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Rhythmic Echoes</t>
+          <t>Echo Nhịp Điệu</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Fan Creation Event Participation</t>
+          <t>Tham Gia Sự Kiện Sáng Tác Người Hâm Mộ</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Chuyện kể trên đảo</t>
+          <t>Huyền Thoại Quần Đảo</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Mua Peach Blossom</t>
+          <t>Mua Hoa Đào</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Tham gia Event Cộng tác Wuthering Waves X Pizza Hut để nhận</t>
+          <t>Tham gia Sự kiện Cộng tác Wuthering Waves X Pizza Hut để nhận</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Cube, Cubic và Cubie</t>
+          <t>Khối, Khối Lập Phương và Cubie</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Among the Clouds</t>
+          <t>Giữa Mây Trời</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Moonlit Haven</t>
+          <t>Nơi Trú Ẩn Dưới Trăng</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Sound of Tides</t>
+          <t>Âm thanh Thủy Triều</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>To the Next Dream</t>
+          <t>Tới Giấc Mơ Kế Tiếp</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>A Whale's Song</t>
+          <t>Khúc Ca Cá Voi</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Noble Exhortation</t>
+          <t>Lời Kêu Gọi Cao Quý</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Cube, Cubic và Cubie</t>
+          <t>Khối, Khối Lập Phương và Cubie</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Destiny Reclaimed</t>
+          <t>Định Mệnh Đã Được Đoạt Lại</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Burning Hunt</t>
+          <t>Săn Lùng Nảy Lửa</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Twilight of Tomorrow</t>
+          <t>Hoàng Hôn Của Ngày Mai</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Dawn Within Amber</t>
+          <t>Bình Minh Trong Hổ Phách</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Traveler From Afar</t>
+          <t>Lữ Khách Phương Xa</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Land Đèn Lồng</t>
+          <t>Vùng Đất Đèn Lồng</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Septimont Fighter</t>
+          <t>Chiến Binh Septimont</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Memories about the Isles</t>
+          <t>Ký ức về Quần đảo</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Sigil: Peach Blossom</t>
+          <t>Ấn Tín: Hoa Đào</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Waves of Flavor</t>
+          <t>Sóng Hương Vị</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Deep Dreams Film Festival</t>
+          <t>Liên Hoan Phim Deep Dreams</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Once Together</t>
+          <t>Một Lúc Nào Đó Ta Đã Ở Bên Nhau</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Card Duelist</t>
+          <t>Đấu thủ Thẻ</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>The Dreamland</t>
+          <t>Xứ Mộng Ảo</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Phantasma Dreamland</t>
+          <t>Vùng Đất Mộng Ảo</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>"Lighthouse and Blake Bloom" Medal</t>
+          <t>"Huy chương "Ngọn hải đăng và Blake Bloom""</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Voyager of the World</t>
+          <t>Người Du Hành Thế Giới</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Lahai-Roi Pioneers</t>
+          <t>Những Tiên Phong Lahai-Roi</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Iron Symphony</t>
+          <t>Bản Giao Hưởng Thép</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Pioneers</t>
+          <t>Những Nhà Tiên Phong</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Fly, Until Snow Melts</t>
+          <t>Bay đi, cho đến khi tuyết tan</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Night Đáng Nhớ</t>
+          <t>Đêm Đáng Nhớ</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Thu thập 800 Lollo Voucher trong "Where Stars Cascade Down".</t>
+          <t>Thu thập 800 Phiếu Lollo trong "Nơi Sao Rơi".</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Favor of Stars</t>
+          <t>Ân Huệ Của Vì Sao</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Moonlit Path</t>
+          <t>Con Đường Ánh Trăng</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Concealed Starlight</t>
+          <t>Ánh Sao Ẩn</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Đạt 3.000 Journey Points trong "Starpaths Intertwined"</t>
+          <t>Đạt 3.000 Điểm Hành Trình trong "Starpaths Intertwined"</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Sunlit Pursuit</t>
+          <t>Đuổi Bắt Dưới Nắng</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Astral Flight</t>
+          <t>Bay Tinh Tú</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Nhận được từ phần thưởng giới hạn thời gian trong "Soar to the Beat."</t>
+          <t>Nhận được từ phần thưởng giới hạn thời gian trong "Bay Theo Nhịp Điệu."</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Past the Endstate: Doomsday Cycle</t>
+          <t>Vượt Qua Chu Kỳ Tận Thế: Điểm Cuối Cùng</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Selling illegal software</t>
+          <t>Buôn bán phần mềm bất hợp pháp</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Log in to the game</t>
+          <t>Đăng nhập vào game</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Spend 180 Waveplates</t>
+          <t>Tiêu hao 180 Bản Tần Số</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Đạt 100 điểm Hoạt động Sổ tay Hướng dẫn</t>
+          <t>Thu thập 100 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Hoàn thành Tacet Field 5 lần.</t>
+          <t>Hoàn thành Tổ Tacet 5 lần.</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Complete Forgery Challenge 5 times</t>
+          <t>Hoàn thành Thử Thách Giả Mạo 5 lần</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Complete Weekly Challenge 2 times</t>
+          <t>Hoàn thành Thử Thách Hàng Tuần 2 lần</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Complete 3 Daily Quests</t>
+          <t>Hoàn thành 3 Nhiệm Vụ Hằng Ngày</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Thu thập 30 vật phẩm sưu tầm</t>
+          <t>Thu thập 30 Vật phẩm sưu tầm</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Triệu Tập 40 times in total</t>
+          <t>Tổng cộng triệu tập 40 lần</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Thu thập 400 Bản Ghi Nguy Hiểm trong Tower of Adversity.</t>
+          <t>Thu thập 400 Bản Ghi Nguy Hiểm trong Tháp Nghịch Cảnh.</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Hoàn thành Companion Story: Daybreak Cuối Cùng.</t>
+          <t>Hoàn thành Câu Chuyện Đồng Hành: Bình Minh Cuối Cùng.</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Complete Companion Stories: Solitary Path</t>
+          <t>Hoàn thành Câu Chuyện Đồng Hành: Con Đường Cô Đơn.</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 5.000 Points Alloy Smelt</t>
+          <t>Thu thập tổng cộng 5.000 Điểm Nấu Luyện Hợp Kim</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Tổng cộng thu thập 30.000 Points Alloy Smelt.</t>
+          <t>Tổng cộng thu thập 30.000 Điểm Nấu Luyện Hợp Kim.</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả nhiệm vụ trong Second Coming of Solaris</t>
+          <t>Hoàn thành tất cả nhiệm vụ trong Sự Trở Lại Của Solaris</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ chính Act VII: Thời Khắc Vạn Niên Tan Băng</t>
+          <t>Hoàn thành Nhiệm vụ chính Chương VII: Thời Khắc Vạn Niên Tan Băng</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Complete Companion Story Immortal Blaze</t>
+          <t>Hoàn thành Câu Chuyện Đồng Hành Ngọn Lửa Bất Tử.</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Get 3,000 Tactical Simulacra Points</t>
+          <t>Nhận 3.000 Điểm Tương Tác Chiến Thuật</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Get 5,000 Tactical Simulacra Points</t>
+          <t>Nhận 5.000 Điểm Tương Tác Chiến Thuật</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Sử dụng Lollo Express 3 lần trong Lollo Campaign</t>
+          <t>Sử dụng Lollo Express 3 lần trong Chiến dịch Lollo</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Hoàn thành Companion Story: Small Wooly, Big Adventures.</t>
+          <t>Hoàn thành Câu Chuyện Đồng Hành: Cừu Nhỏ, Đại Phiêu Lưu.</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Đạt 30.000 Tactic Points trong Infinite Battle Simulation.</t>
+          <t>Đạt 30.000 Điểm Chiến Thuật trong Mô Phỏng Chiến Đấu Vô Tận.</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Sử dụng Lollo Express 3 lần trong Lollo Campaign: Tái diễn</t>
+          <t>Sử dụng Lollo Express 3 lần trong Chiến dịch Lollo: Tái diễn</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Hoàn thành Companion Story: Ngã Ba Giữa Các Vì Sao.</t>
+          <t>Hoàn thành Câu Chuyện Đồng Hành: Ngã Ba Giữa Các Vì Sao.</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Nhận Rewards tại Tinh Thể Tàn Dư trong Vực Ảo Tưởng 6 lần</t>
+          <t>Nhận thưởng tại Tinh Thể Tàn Dư trong Vực Ảo Tưởng 6 lần</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Đạt 4.000 điểm trong Endless Arena của Chiến Binh Chiến Thuật Cấp I.</t>
+          <t>Đạt 4.000 điểm trong Đấu Trường Vô Tận của Chiến Binh Chiến Thuật Cấp I.</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Đạt 4.000 điểm trong Endless Arena của Chiến Binh Chiến Thuật Cấp II.</t>
+          <t>Đạt 4.000 điểm trong Đấu Trường Vô Tận của Chiến Binh Chiến Thuật Cấp II.</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Đạt 2.600 điểm ở Stage 6 của Tactical Simulacra II.</t>
+          <t>Đạt 2.600 điểm ở Giai Đoạn 6 của Tactical Simulacra II.</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Hoàn thành Companion Story "Nếu Một Night Rainy Có Người Thân".</t>
+          <t>Hoàn thành Câu Chuyện Đồng Hành "Nếu Một Đêm Mưa Có Người Thân".</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Hoàn thành Companion Story "Đêm Đầy Sao".</t>
+          <t>Hoàn thành Câu Chuyện Đồng Hành "Đêm Đầy Sao".</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Đạt 8.000 điểm trong Echo Car Driver của John Wicktorio: Không Debts for Old Men</t>
+          <t>Đạt 8.000 điểm trong Echo Car Driver của John Wicktorio: No Debts for Old Men</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Tactical Hologram Hoàn Chỉnh: Nỗi Đau Ảo - Fallacy of Không Return IV.</t>
+          <t>Bản Hologram Chiến Thuật Hoàn Chỉnh: Nỗi Đau Ảo - Ảo Tưởng Vô Hồi IV.</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Hoàn thành Tactical Hologram: Phantom Pain - Sentry Construct IV</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Phantom Pain - Sentry Construct IV</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Đồng Hành "Giấc Mộng Night Ngắn Ngủi".</t>
+          <t>Hoàn thành Nhiệm Vụ Đồng Hành "Giấc Mộng Đêm Ngắn Ngủi".</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Thu thập 1.500 Matrix Crystal trong "Virtual Crisis: Prototype Trials"</t>
+          <t>Thu thập 1.500 Tinh Thể Ma Trận trong "Khủng Hoảng Ảo: Thử Nghiệm Nguyên Mẫu"</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Đạt 1.000 điểm trong Whimpering Wastes Vô Tận.</t>
+          <t>Đạt 1.000 điểm trong Vùng Đất Than Khóc Vô Tận.</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Nhận tất cả phần thưởng trong Lollo Campaign: Hành Trình Set Sail.</t>
+          <t>Nhận tất cả phần thưởng trong Chiến dịch Lollo: Hành Trình Khởi Hành.</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Đạt 12.000 điểm trong If Bạn Gaze Into the Abyss of Dreams.</t>
+          <t>Đạt 12.000 điểm trong If You Gaze Into the Abyss of Dreams.</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Main "Dawn Đứng Lặng Trên Vùng Đất Hoang"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Bình Minh Đứng Lặng Trên Vùng Đất Hoang"</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Main "Starlight Lấp Lánh Trong Mống Mắt"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Ánh Sao Lấp Lánh Trong Mống Mắt"</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Main "Khúc Ca Sunrise Thứ Hai"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Khúc Ca Bình Minh Thứ Hai"</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Exploration 8 trong "Lahai-Roi Pioneers"</t>
+          <t>Đạt Cấp Độ Thám Hiểm 8 trong "Lahai-Roi Pioneers"</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 8 trong "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Đạt Cấp Bậc 8 trong "Đỉnh Danh Vọng: Duel Tái Sinh"</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Exploration 5 trong "Lahai-Roi Pioneers"</t>
+          <t>Đạt Cấp Độ Thám Hiểm 5 trong "Lahai-Roi Pioneers"</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Đạt Cấp Cảm Xúc 8 trong sự kiện "Where Stars Cascade Down".</t>
+          <t>Đạt Cấp Cảm Xúc 8 trong sự kiện "Nơi Sao Rơi".</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Nhận tất cả phần thưởng trong sự kiện "Lollo Campaign: Triển Khai".</t>
+          <t>Nhận tất cả phần thưởng trong sự kiện "Chiến dịch Lollo: Triển Khai".</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Tempest Mephis</t>
+          <t>Hologram Chiến Thuật: Tempest Mephis</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Impermanence Heron</t>
+          <t>Hologram Chiến Thuật: Impermanence Heron</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Mourning Aix</t>
+          <t>Hologram Chiến Thuật: Mourning Aix</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Feilian Beringal</t>
+          <t>Bản Hologram Chiến Thuật: Feilian Beringal</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Crownless</t>
+          <t>Bản Hologram Chiến Thuật: Crownless</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Inferno Rider</t>
+          <t>Hologram Chiến Thuật: Inferno Rider</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Phantom Pain</t>
+          <t>Hologram Chiến Thuật: Nỗi Đau Ảo Ảnh</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Synchronization</t>
+          <t>Hologram Chiến Thuật: Đồng Bộ Hóa</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Không special mechanism</t>
+          <t>Không có cơ chế đặc biệt</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Difficulty I</t>
+          <t>Độ khó I</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Difficulty II</t>
+          <t>Độ khó II</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Difficulty III</t>
+          <t>Độ Khó III</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Difficulty IV</t>
+          <t>Độ Khó IV</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Difficulty V</t>
+          <t>Độ Khó V</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Difficulty VI</t>
+          <t>Độ Khó VI</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Fallacy of Không Return</t>
+          <t>Ảo Tưởng Vô Hồi</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Sentry Construct</t>
+          <t>Công Trình Tuần Tra</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Dragon Than Khóc</t>
+          <t>Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Lady of the Sea</t>
+          <t>Nữ Thần Biển Cả</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Sư Tử Glory - Giai Đoạn Truy Cập Sớm</t>
+          <t>Sư Tử Vinh Quang - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>The False Sovereign</t>
+          <t>Kẻ Quân Vương Giả Mạo</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Invalid redemption code</t>
+          <t>Mã đổi không hợp lệ</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Please enter the redemption code</t>
+          <t>Vui lòng nhập mã đổi quà</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Input length is too short</t>
+          <t>Nội dung nhập quá ngắn</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Round 1 Report</t>
+          <t>Báo cáo Vòng 1</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Round 10 Report</t>
+          <t>Báo cáo Vòng 10</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Round 11 Report</t>
+          <t>Báo cáo Vòng 11</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Round 12 Report</t>
+          <t>Báo cáo Vòng 12</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Round 2 Report</t>
+          <t>Báo cáo Vòng 2</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Round 3 Report</t>
+          <t>Báo cáo Vòng 3</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Round 4 Report</t>
+          <t>Báo cáo Vòng 4</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Round 5 Report</t>
+          <t>Báo cáo Vòng 5</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Round 6 Report</t>
+          <t>Báo cáo Vòng 6</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Round 7 Report</t>
+          <t>Báo cáo Vòng 7</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Round 8 Report</t>
+          <t>Báo cáo Vòng 8</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Round 9 Report</t>
+          <t>Báo cáo Vòng 9</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Gain double rewards</t>
+          <t>Nhận phần thưởng gấp đôi.</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
